--- a/data/vendor-search/results_all_doorbell.xlsx
+++ b/data/vendor-search/results_all_doorbell.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>cpe_strings</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>matched_terms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -472,8 +477,10 @@
       <c r="D2" t="n">
         <v>4.6</v>
       </c>
-      <c r="E2" t="n">
-        <v>3</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -483,6 +490,11 @@
       <c r="G2" t="inlineStr">
         <is>
           <t>cpe:2.3:o:ring:ring_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ring:ring:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>video doorbell</t>
         </is>
       </c>
     </row>
@@ -505,8 +517,10 @@
       <c r="D3" t="n">
         <v>9.1</v>
       </c>
-      <c r="E3" t="n">
-        <v>3</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -516,6 +530,11 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>cpe:2.3:o:amazon:ring_video_doorbell_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:amazon:ring_video_doorbell:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ring doorbell</t>
         </is>
       </c>
     </row>
@@ -538,8 +557,10 @@
       <c r="D4" t="n">
         <v>7.2</v>
       </c>
-      <c r="E4" t="n">
-        <v>3</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -549,6 +570,11 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>cpe:2.3:o:akuvox:sp-r50p_firmware:50.0.6.156:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:sp-r50p:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>akuvox</t>
         </is>
       </c>
     </row>
@@ -571,8 +597,10 @@
       <c r="D5" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E5" t="n">
-        <v>3</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -582,6 +610,11 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>cpe:2.3:o:akuvox:sp-r50p_firmware:50.0.6.156:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:sp-r50p:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>akuvox</t>
         </is>
       </c>
     </row>
@@ -604,8 +637,10 @@
       <c r="D6" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E6" t="n">
-        <v>3</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -615,6 +650,11 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>cpe:2.3:o:akuvox:sp-r50p_firmware:50.0.6.156:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:sp-r50p:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>akuvox</t>
         </is>
       </c>
     </row>
@@ -637,8 +677,10 @@
       <c r="D7" t="n">
         <v>4.6</v>
       </c>
-      <c r="E7" t="n">
-        <v>3.1</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -648,6 +690,11 @@
       <c r="G7" t="inlineStr">
         <is>
           <t>cpe:2.3:o:fermax:outdoor_panel_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:fermax:outdoor_panel:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>fermax</t>
         </is>
       </c>
     </row>
@@ -670,8 +717,10 @@
       <c r="D8" t="n">
         <v>6.5</v>
       </c>
-      <c r="E8" t="n">
-        <v>3.1</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -681,6 +730,11 @@
       <c r="G8" t="inlineStr">
         <is>
           <t>cpe:2.3:o:aiphone:gt-dmb-n_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:aiphone:gt-dmb-n:-:*:*:*:*:*:*:*|cpe:2.3:o:aiphone:gt-dmb_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:aiphone:gt-dmb:-:*:*:*:*:*:*:*|cpe:2.3:o:aiphone:gt-dmb-lvn_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:aiphone:gt-dmb-lvn:-:*:*:*:*:*:*:*|cpe:2.3:o:aiphone:gt-db-vn_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:aiphone:gt-db-vn:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>aiphone</t>
         </is>
       </c>
     </row>
@@ -703,8 +757,10 @@
       <c r="D9" t="n">
         <v>7.5</v>
       </c>
-      <c r="E9" t="n">
-        <v>3.1</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -714,6 +770,11 @@
       <c r="G9" t="inlineStr">
         <is>
           <t>cpe:2.3:o:akuvox:e11_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:e11:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>akuvox</t>
         </is>
       </c>
     </row>
@@ -736,8 +797,10 @@
       <c r="D10" t="n">
         <v>7.5</v>
       </c>
-      <c r="E10" t="n">
-        <v>3.1</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -745,6 +808,11 @@
           <t>cpe:2.3:o:akuvox:e11_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:e11:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>akuvox</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -765,8 +833,10 @@
       <c r="D11" t="n">
         <v>7.5</v>
       </c>
-      <c r="E11" t="n">
-        <v>3.1</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -774,6 +844,11 @@
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>fermax</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -794,8 +869,10 @@
       <c r="D12" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E12" t="n">
-        <v>3.1</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -805,6 +882,11 @@
       <c r="G12" t="inlineStr">
         <is>
           <t>cpe:2.3:o:dbell:db01-s_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:dbell:db01-s:gen_1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>video doorbell</t>
         </is>
       </c>
     </row>
@@ -827,8 +909,10 @@
       <c r="D13" t="n">
         <v>6.6</v>
       </c>
-      <c r="E13" t="n">
-        <v>3.1</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -838,6 +922,11 @@
       <c r="G13" t="inlineStr">
         <is>
           <t>cpe:2.3:o:siedle:sg_150-0_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:siedle:sg_150-0:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>siedle</t>
         </is>
       </c>
     </row>
@@ -860,8 +949,10 @@
       <c r="D14" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E14" t="n">
-        <v>3.1</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -871,6 +962,11 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>cpe:2.3:o:siedle:sg_150-0_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:siedle:sg_150-0:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>siedle</t>
         </is>
       </c>
     </row>
@@ -893,8 +989,10 @@
       <c r="D15" t="n">
         <v>7</v>
       </c>
-      <c r="E15" t="n">
-        <v>3.1</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -904,6 +1002,11 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>cpe:2.3:o:siedle:sg_150-0_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:siedle:sg_150-0:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>siedle</t>
         </is>
       </c>
     </row>
@@ -926,8 +1029,10 @@
       <c r="D16" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E16" t="n">
-        <v>3.1</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -937,6 +1042,11 @@
       <c r="G16" t="inlineStr">
         <is>
           <t>cpe:2.3:a:commax:cdp-1020mb_firmware:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>commax</t>
         </is>
       </c>
     </row>
@@ -959,8 +1069,10 @@
       <c r="D17" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E17" t="n">
-        <v>3.1</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -970,6 +1082,11 @@
       <c r="G17" t="inlineStr">
         <is>
           <t>cpe:2.3:o:adt:lifeshield_diy_hd_video_doorbell_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:adt:lifeshield_diy_hd_video_doorbell:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>video doorbell</t>
         </is>
       </c>
     </row>
@@ -992,8 +1109,10 @@
       <c r="D18" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E18" t="n">
-        <v>3.1</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1003,6 +1122,11 @@
       <c r="G18" t="inlineStr">
         <is>
           <t>cpe:2.3:o:akuvox:c315_firmware:115.116.2613:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:c315:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>akuvox</t>
         </is>
       </c>
     </row>
@@ -1025,8 +1149,10 @@
       <c r="D19" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E19" t="n">
-        <v>3.1</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1036,6 +1162,11 @@
       <c r="G19" t="inlineStr">
         <is>
           <t>cpe:2.3:a:comelitgroup:away_from_home:2.8.0:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>comelit</t>
         </is>
       </c>
     </row>
@@ -1058,8 +1189,10 @@
       <c r="D20" t="n">
         <v>6.5</v>
       </c>
-      <c r="E20" t="n">
-        <v>3.1</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1069,6 +1202,11 @@
       <c r="G20" t="inlineStr">
         <is>
           <t>cpe:2.3:o:nightowlsp:smart_doorbell_firmware:20190505:*:*:*:*:*:*:*|cpe:2.3:h:nightowlsp:smart_doorbell:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>smart doorbell</t>
         </is>
       </c>
     </row>
@@ -1091,8 +1229,10 @@
       <c r="D21" t="n">
         <v>7.5</v>
       </c>
-      <c r="E21" t="n">
-        <v>3.1</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
@@ -1100,6 +1240,11 @@
           <t>cpe:2.3:o:akuvox:e11_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:e11:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>akuvox</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1120,8 +1265,10 @@
       <c r="D22" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E22" t="n">
-        <v>3.1</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
@@ -1129,6 +1276,11 @@
           <t>cpe:2.3:o:akuvox:e11_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:e11:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>akuvox</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1149,8 +1301,10 @@
       <c r="D23" t="n">
         <v>7.5</v>
       </c>
-      <c r="E23" t="n">
-        <v>3.1</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
@@ -1158,6 +1312,11 @@
           <t>cpe:2.3:o:akuvox:e11_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:e11:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>akuvox</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1178,8 +1337,10 @@
       <c r="D24" t="n">
         <v>5.3</v>
       </c>
-      <c r="E24" t="n">
-        <v>3.1</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
@@ -1187,6 +1348,11 @@
           <t>cpe:2.3:o:akuvox:e11_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:e11:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>akuvox</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1207,8 +1373,10 @@
       <c r="D25" t="n">
         <v>7.5</v>
       </c>
-      <c r="E25" t="n">
-        <v>3.1</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
@@ -1216,6 +1384,11 @@
           <t>cpe:2.3:o:akuvox:e11_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:e11:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>akuvox</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1236,8 +1409,10 @@
       <c r="D26" t="n">
         <v>9.1</v>
       </c>
-      <c r="E26" t="n">
-        <v>3.1</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
@@ -1245,6 +1420,11 @@
           <t>cpe:2.3:o:akuvox:e11_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:e11:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>akuvox</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1265,8 +1445,10 @@
       <c r="D27" t="n">
         <v>6.5</v>
       </c>
-      <c r="E27" t="n">
-        <v>3.1</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1276,6 +1458,11 @@
       <c r="G27" t="inlineStr">
         <is>
           <t>cpe:2.3:o:akuvox:e11_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:e11:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>akuvox</t>
         </is>
       </c>
     </row>
@@ -1298,8 +1485,10 @@
       <c r="D28" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E28" t="n">
-        <v>3.1</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1309,6 +1498,11 @@
       <c r="G28" t="inlineStr">
         <is>
           <t>cpe:2.3:o:akuvox:e11_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:e11:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>akuvox</t>
         </is>
       </c>
     </row>
@@ -1331,8 +1525,10 @@
       <c r="D29" t="n">
         <v>9.1</v>
       </c>
-      <c r="E29" t="n">
-        <v>3.1</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
@@ -1340,6 +1536,11 @@
           <t>cpe:2.3:o:akuvox:e11_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:e11:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>akuvox</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1360,8 +1561,10 @@
       <c r="D30" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E30" t="n">
-        <v>3.1</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
@@ -1369,6 +1572,11 @@
           <t>cpe:2.3:o:akuvox:e11_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:e11:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>akuvox</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1389,8 +1597,10 @@
       <c r="D31" t="n">
         <v>9.1</v>
       </c>
-      <c r="E31" t="n">
-        <v>3.1</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
@@ -1398,6 +1608,11 @@
           <t>cpe:2.3:o:akuvox:e11_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:e11:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>akuvox</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1418,8 +1633,10 @@
       <c r="D32" t="n">
         <v>8</v>
       </c>
-      <c r="E32" t="n">
-        <v>3</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1427,6 +1644,11 @@
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>aiphone</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1447,8 +1669,10 @@
       <c r="D33" t="n">
         <v>6.5</v>
       </c>
-      <c r="E33" t="n">
-        <v>3</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1456,6 +1680,11 @@
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>aiphone</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1476,8 +1705,10 @@
       <c r="D34" t="n">
         <v>5.4</v>
       </c>
-      <c r="E34" t="n">
-        <v>3</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1485,6 +1716,11 @@
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>aiphone</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1505,8 +1741,10 @@
       <c r="D35" t="n">
         <v>5.5</v>
       </c>
-      <c r="E35" t="n">
-        <v>3</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1514,6 +1752,11 @@
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>aiphone</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1534,11 +1777,18 @@
       <c r="D36" t="n">
         <v>7.5</v>
       </c>
-      <c r="E36" t="n">
-        <v>3.1</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>video doorbell</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1559,8 +1809,10 @@
       <c r="D37" t="n">
         <v>5.3</v>
       </c>
-      <c r="E37" t="n">
-        <v>3.1</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1568,6 +1820,11 @@
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>video doorbell</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1588,8 +1845,10 @@
       <c r="D38" t="n">
         <v>5.3</v>
       </c>
-      <c r="E38" t="n">
-        <v>3.1</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1597,6 +1856,11 @@
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>video doorbell</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1617,8 +1881,10 @@
       <c r="D39" t="n">
         <v>6.5</v>
       </c>
-      <c r="E39" t="n">
-        <v>3.1</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1626,6 +1892,11 @@
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>video doorbell</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1646,8 +1917,10 @@
       <c r="D40" t="n">
         <v>7.3</v>
       </c>
-      <c r="E40" t="n">
-        <v>3.1</v>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1657,6 +1930,11 @@
       <c r="G40" t="inlineStr">
         <is>
           <t>cpe:2.3:o:reolink:smart_2k\+_plug-in_wi-fi_video_doorbell_with_chime_firmware:3.0.0.4662_2503122283:*:*:*:*:*:*:*|cpe:2.3:h:reolink:smart_2k\+_plug-in_wi-fi_video_doorbell_with_chime:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>video doorbell</t>
         </is>
       </c>
     </row>
@@ -1679,8 +1957,10 @@
       <c r="D41" t="n">
         <v>4</v>
       </c>
-      <c r="E41" t="n">
-        <v>3.1</v>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1688,6 +1968,11 @@
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>video doorbell</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1708,8 +1993,10 @@
       <c r="D42" t="n">
         <v>7.5</v>
       </c>
-      <c r="E42" t="n">
-        <v>3.1</v>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1719,6 +2006,11 @@
       <c r="G42" t="inlineStr">
         <is>
           <t>cpe:2.3:o:reolink:smart_2k\+_plug-in_wi-fi_video_doorbell_with_chime_firmware:3.0.0.4662_2503122283:*:*:*:*:*:*:*|cpe:2.3:h:reolink:smart_2k\+_plug-in_wi-fi_video_doorbell_with_chime:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>video doorbell</t>
         </is>
       </c>
     </row>
@@ -1741,8 +2033,10 @@
       <c r="D43" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E43" t="n">
-        <v>3.1</v>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1752,6 +2046,11 @@
       <c r="G43" t="inlineStr">
         <is>
           <t>cpe:2.3:o:reolink:smart_2k\+_plug-in_wi-fi_video_doorbell_with_chime_firmware:3.0.0.4662_2503122283:*:*:*:*:*:*:*|cpe:2.3:h:reolink:smart_2k\+_plug-in_wi-fi_video_doorbell_with_chime:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>video doorbell</t>
         </is>
       </c>
     </row>
@@ -1774,8 +2073,10 @@
       <c r="D44" t="n">
         <v>3.5</v>
       </c>
-      <c r="E44" t="n">
-        <v>3.1</v>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1783,6 +2084,11 @@
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>video doorbell</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1803,8 +2109,10 @@
       <c r="D45" t="n">
         <v>5.1</v>
       </c>
-      <c r="E45" t="n">
-        <v>3.1</v>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1812,6 +2120,11 @@
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>video doorbell</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1832,8 +2145,10 @@
       <c r="D46" t="n">
         <v>6.8</v>
       </c>
-      <c r="E46" t="n">
-        <v>3.1</v>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1841,6 +2156,11 @@
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>video doorbell</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1861,8 +2181,10 @@
       <c r="D47" t="n">
         <v>8</v>
       </c>
-      <c r="E47" t="n">
-        <v>3</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1870,6 +2192,11 @@
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>video doorbell</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1890,8 +2217,10 @@
       <c r="D48" t="n">
         <v>7.5</v>
       </c>
-      <c r="E48" t="n">
-        <v>3.1</v>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1899,6 +2228,11 @@
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>video doorbell</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1924,6 +2258,11 @@
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>commax</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1949,6 +2288,11 @@
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>commax</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1974,6 +2318,11 @@
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>commax</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1999,6 +2348,11 @@
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>commax</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2024,6 +2378,11 @@
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>commax</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2049,6 +2408,11 @@
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>commax</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2074,6 +2438,11 @@
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>commax</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2094,8 +2463,10 @@
       <c r="D56" t="n">
         <v>5.3</v>
       </c>
-      <c r="E56" t="n">
-        <v>3.1</v>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2105,6 +2476,11 @@
       <c r="G56" t="inlineStr">
         <is>
           <t>cpe:2.3:o:akuvox:s539_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:s539:-:*:*:*:*:*:*:*|cpe:2.3:o:akuvox:s532_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:s532:-:*:*:*:*:*:*:*|cpe:2.3:o:akuvox:x916_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:x916:-:*:*:*:*:*:*:*|cpe:2.3:o:akuvox:x915_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:x915:-:*:*:*:*:*:*:*|cpe:2.3:o:akuvox:x912_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:x912:-:*:*:*:*:*:*:*|cpe:2.3:o:akuvox:r29_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:r29:-:*:*:*:*:*:*:*|cpe:2.3:o:akuvox:r20k-2_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:r20k-2:-:*:*:*:*:*:*:*|cpe:2.3:o:akuvox:r20a-2_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:r20a-2:-:*:*:*:*:*:*:*|cpe:2.3:o:akuvox:c313w-2_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:c313w-2:-:*:*:*:*:*:*:*|cpe:2.3:o:akuvox:ns-2_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:ns-2:-:*:*:*:*:*:*:*|cpe:2.3:o:akuvox:nc-2_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:nc-2:-:*:*:*:*:*:*:*|cpe:2.3:o:akuvox:nx-2_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:nx-2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>akuvox</t>
         </is>
       </c>
     </row>
@@ -2127,8 +2503,10 @@
       <c r="D57" t="n">
         <v>4.3</v>
       </c>
-      <c r="E57" t="n">
-        <v>3.1</v>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2138,6 +2516,11 @@
       <c r="G57" t="inlineStr">
         <is>
           <t>cpe:2.3:o:akuvox:s539_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:s539:-:*:*:*:*:*:*:*|cpe:2.3:o:akuvox:s532_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:s532:-:*:*:*:*:*:*:*|cpe:2.3:o:akuvox:x916_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:x916:-:*:*:*:*:*:*:*|cpe:2.3:o:akuvox:x915_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:x915:-:*:*:*:*:*:*:*|cpe:2.3:o:akuvox:x912_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:x912:-:*:*:*:*:*:*:*|cpe:2.3:o:akuvox:r29_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:r29:-:*:*:*:*:*:*:*|cpe:2.3:o:akuvox:e16c_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:e16c:-:*:*:*:*:*:*:*|cpe:2.3:o:akuvox:r20k-2_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:r20k-2:-:*:*:*:*:*:*:*|cpe:2.3:o:akuvox:r20a-2_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:r20a-2:-:*:*:*:*:*:*:*|cpe:2.3:o:akuvox:c313w-2_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:c313w-2:-:*:*:*:*:*:*:*|cpe:2.3:o:akuvox:ns-2_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:ns-2:-:*:*:*:*:*:*:*|cpe:2.3:o:akuvox:nc-2_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:nc-2:-:*:*:*:*:*:*:*|cpe:2.3:o:akuvox:nx-2_firmware:912.30.1.137:*:*:*:*:*:*:*|cpe:2.3:h:akuvox:nx-2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>akuvox</t>
         </is>
       </c>
     </row>
@@ -2160,8 +2543,10 @@
       <c r="D58" t="n">
         <v>6.1</v>
       </c>
-      <c r="E58" t="n">
-        <v>3.1</v>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2169,6 +2554,11 @@
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>commax</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2189,8 +2579,10 @@
       <c r="D59" t="n">
         <v>5.3</v>
       </c>
-      <c r="E59" t="n">
-        <v>3.1</v>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2198,6 +2590,11 @@
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>video doorbell</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
